--- a/Project/Aspen/Aspen/hydrocracking.xlsx
+++ b/Project/Aspen/Aspen/hydrocracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Alessio/Library/CloudStorage/OneDrive-PolitecnicodiTorino/PhD/Condivise/Power to X/FT/TEA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamis\Desktop\Masters Project\Economics Code\AspenPlus-Python-Interface\Project\Aspen\Aspen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A612F78-2E9C-3341-B69B-C5EB2C8557CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED932542-D609-4B01-B35D-A70B570DF3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="28800" windowHeight="16620" activeTab="4" xr2:uid="{7B515793-712E-2E47-913B-AE04468B403F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7B515793-712E-2E47-913B-AE04468B403F}"/>
   </bookViews>
   <sheets>
     <sheet name="Inlet" sheetId="7" r:id="rId1"/>
@@ -49,7 +49,7 @@
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <pivotCaches>
-    <pivotCache cacheId="283" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -720,8 +720,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -752,7 +752,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1126,7 +1126,7 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="92"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="0.00E+00">
                   <c:v>7.1114470114353595E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -1145,7 +1145,7 @@
                   <c:v>1.1449167841188555E-8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.1451006160106345E-2</c:v>
+                  <c:v>5.2157349925587217E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8.7688471000871231E-5</c:v>
@@ -1506,7 +1506,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1602,7 +1602,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1994,7 +1994,7 @@
                   <c:v>1.6611306944078475E-8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.7053693992314714E-2</c:v>
+                  <c:v>6.7760037757795585E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1.0153018821769684E-4</c:v>
@@ -2451,7 +2451,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5695,7 +5695,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{241862BD-75CB-2747-B5D5-7068357C4E77}" name="Tabella pivot12" cacheId="283" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{241862BD-75CB-2747-B5D5-7068357C4E77}" name="Tabella pivot12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="J7:M35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -5876,7 +5876,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -6193,12 +6193,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12AC68F-1B8B-7B40-94E4-0A00BC5EB388}">
   <dimension ref="B2:N97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>93</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>1.52099389042742E-2</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>94</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>3.7286654227742101E-3</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>5.94540454937842</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>2.1638773442802702E-6</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>7.1114470114353595E-4</v>
       </c>
       <c r="F6" s="10">
-        <f t="shared" si="0"/>
+        <f>+D6/SUM($D$2:$D$73)</f>
         <v>1.1440168875881178E-4</v>
       </c>
       <c r="G6" s="9">
@@ -6292,7 +6292,7 @@
         <v>4.7211617270082202E-5</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>6.7118241360494097E-4</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>5.2042265742511498E-4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>6.6226843020797E-3</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>7.1638573419931302E-10</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>1.03661201043437E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>9</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>3.3472162121052003E-5</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>10</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>3.9540471843395002E-23</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>11</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>8.1042985212580205E-3</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>96</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>2.9194138897124003E-4</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>2.6819903246205801E-20</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>98</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>5.0503086454164202E-5</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>2.3906005494957702E-3</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>14</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>2.6500938700863598E-3</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>15</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>6.4063035314008997E-18</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>1.7247701590080299E-19</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>100</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>1.4990394317496801E-4</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>8.2387548743203295E-4</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>17</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>1.07199655047712E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>18</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>7.9674531420183096E-16</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>19</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>4.9518935837685497E-16</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>101</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>1.4269671095117401E-4</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>20</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>5.6624956704961799E-4</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>21</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>3.8776176921933003E-4</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>22</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>3.3072995427325399E-13</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>23</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>2.5845622836709602E-4</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>24</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>1.63664818963812E-12</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>25</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>9.3246114119913899E-5</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>26</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>2.4498764717348099E-4</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>27</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>1.3342546240044501E-11</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>28</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>7.2635867073766097E-5</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>29</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>3.3006129466458802E-9</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>30</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>4.3590737311418802E-5</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>31</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>3.09364616306399E-5</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>32</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>1.23755496537252E-8</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>33</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>1.2653118615531299E-5</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>34</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>2.4472592052592002E-7</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>35</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>4.6774426735821001E-6</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>36</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>8.6634522667096404E-7</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>37</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>1.33773057924035E-7</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>102</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>2.21141186502629E-7</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>38</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>8.67717398136949E-7</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>39</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>3.30029121117328E-6</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>40</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>9.9387069544041203E-8</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>41</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>4.19811895295621E-7</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>103</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>7.0009672674421295E-8</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>42</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>1.3318120127572001E-6</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>43</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>1.60785472524846E-7</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>44</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>8.4421857706400597E-6</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>45</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>1.2060739846348E-6</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>104</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>3.6328074533291697E-5</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>105</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>7.4155414988475903E-6</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>48</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>1.3851608285691801E-4</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>49</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>5.3100417751653098E-5</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>50</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>5.1537285160403496E-4</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>51</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>4.1789278002443503E-5</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>52</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>2.5040211067318902E-3</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>53</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>2.3369626324977601E-2</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>54</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>1.9695471401849799E-2</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>55</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>1.6175175478444E-2</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>56</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>1.3600303538192599E-2</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>57</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>1.2066879670281999E-2</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>58</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>1.1284423009686999E-2</v>
       </c>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>59</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>1.2394427258106799E-2</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>60</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>1.6686778562321002E-2</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>61</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>2.2425891616831398E-2</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>62</v>
       </c>
@@ -7766,76 +7766,76 @@
         <v>9.6126590674868902E-3</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="3"/>
     </row>
   </sheetData>
@@ -7846,9 +7846,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E28FF3F4-9D57-4B42-B99E-BB9DEDB2C6F9}">
   <dimension ref="A1:CY96"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>89</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.4</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <f>+Inlet!D8</f>
         <v>2.5701200645325E-3</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <f>+Inlet!D9</f>
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <f>+Inlet!D10</f>
         <v>2.3793870260887098E-2</v>
@@ -8308,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <f>+Inlet!D11</f>
         <v>2.8280897263054401E-9</v>
@@ -8340,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <f>+Inlet!D12</f>
         <v>2.26564734726744E-2</v>
@@ -8363,7 +8363,7 @@
         <v>2.26564734726744E-2</v>
       </c>
       <c r="CV8">
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="CW8" s="2" t="s">
         <v>8</v>
@@ -8372,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <f>+Inlet!D13</f>
         <v>6.5688059618994703E-5</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <f>+Inlet!D14</f>
         <v>8.1154749464936498E-23</v>
@@ -8412,8 +8412,8 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
+      <c r="E10" s="5">
+        <f>B10</f>
         <v>8.1154749464936498E-23</v>
       </c>
       <c r="F10" s="1">
@@ -8436,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <f>+Inlet!D15</f>
         <v>1.24311871132496E-2</v>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <f>+Inlet!D16</f>
         <v>7.9740251659888401E-4</v>
@@ -8498,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <f>+Inlet!D17</f>
         <v>4.9454120758277598E-20</v>
@@ -8530,7 +8530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <f>+Inlet!D18</f>
         <v>7.7846204715078602E-5</v>
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <f>+Inlet!D19</f>
         <v>2.94082363397296E-3</v>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <f>+Inlet!D20</f>
         <v>4.7346598724411996E-3</v>
@@ -8624,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <f>+Inlet!D21</f>
         <v>1.63131923146749E-17</v>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <f>+Inlet!D22</f>
         <v>4.3282018242143298E-19</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <f>+Inlet!D23</f>
         <v>2.0961080448768401E-4</v>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <f>+Inlet!D24</f>
         <v>1.1693698851101501E-3</v>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <f>+Inlet!D25</f>
         <v>1.44797760949513E-3</v>
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <f>+Inlet!D26</f>
         <v>1.61549255798959E-15</v>
@@ -8833,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <f>+Inlet!D27</f>
         <v>1.1090436396881701E-15</v>
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <f>+Inlet!D28</f>
         <v>1.9452524184119399E-4</v>
@@ -8907,17 +8907,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B25" s="5">
         <f>+Inlet!D29</f>
         <v>7.8531933495412805E-4</v>
       </c>
       <c r="C25">
-        <f t="shared" si="8"/>
+        <f>(EXP($A$3*(F25-7))-1)/(EXP($A$3*(18-7))-1)</f>
         <v>6.1133547195051296E-3</v>
       </c>
       <c r="D25">
-        <f t="shared" si="6"/>
+        <f>1/(F25-6)*C25</f>
         <v>3.0566773597525648E-3</v>
       </c>
       <c r="E25" s="5">
@@ -8934,9 +8934,9 @@
         <f>+E25</f>
         <v>2.4004678313302243E-6</v>
       </c>
-      <c r="N25">
-        <f>+E25*2</f>
-        <v>4.8009356626604486E-6</v>
+      <c r="N25" s="5">
+        <f>B2</f>
+        <v>7.1114470114353595E-4</v>
       </c>
       <c r="Q25" s="5">
         <f>+E25</f>
@@ -8954,10 +8954,10 @@
       </c>
       <c r="CY25">
         <f>SUM(L25:S25)/2</f>
-        <v>4.8009356626604486E-6</v>
-      </c>
-    </row>
-    <row r="26" spans="2:103" x14ac:dyDescent="0.2">
+        <v>3.5797281840309824E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <f>+Inlet!D30</f>
         <v>5.23018392722026E-4</v>
@@ -8970,8 +8970,8 @@
         <f t="shared" si="6"/>
         <v>3.0566773597525648E-3</v>
       </c>
-      <c r="E26">
-        <f t="shared" ref="E26:E85" si="10">1/(F26-6)*C26*B26</f>
+      <c r="E26" s="5">
+        <f>1/(F26-6)*C26*B26</f>
         <v>1.5986984797675924E-6</v>
       </c>
       <c r="F26" s="1">
@@ -9003,17 +9003,17 @@
         <v>21</v>
       </c>
       <c r="CY26">
-        <f t="shared" ref="CY26:CY35" si="11">SUM(L26:AA26)/2</f>
+        <f t="shared" ref="CY26:CY35" si="10">SUM(L26:AA26)/2</f>
         <v>3.1973969595351848E-6</v>
       </c>
     </row>
-    <row r="27" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B27" s="5">
         <f>+Inlet!D31</f>
         <v>6.7110389592260004E-13</v>
       </c>
       <c r="C27">
-        <f t="shared" si="5"/>
+        <f>(EXP($A$3*(F27-7))-1)/(EXP($A$3*(18-7))-1)</f>
         <v>6.1133547195051296E-3</v>
       </c>
       <c r="D27">
@@ -9021,7 +9021,7 @@
         <v>3.0566773597525648E-3</v>
       </c>
       <c r="E27">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E26:E85" si="11">1/(F27-6)*C27*B27</f>
         <v>2.051348084708353E-15</v>
       </c>
       <c r="F27" s="1">
@@ -9053,11 +9053,11 @@
         <v>22</v>
       </c>
       <c r="CY27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4.1026961694167061E-15</v>
       </c>
     </row>
-    <row r="28" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <f>+Inlet!D32</f>
         <v>3.6401436079514898E-4</v>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F28" s="1">
@@ -9090,11 +9090,11 @@
         <v>23</v>
       </c>
       <c r="CY28">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:103" x14ac:dyDescent="0.2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B29" s="5">
         <f>+Inlet!D33</f>
         <v>3.55320707761801E-12</v>
@@ -9107,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F29" s="1">
@@ -9127,11 +9127,11 @@
         <v>24</v>
       </c>
       <c r="CY29">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:103" x14ac:dyDescent="0.2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <f>+Inlet!D34</f>
         <v>1.3366580259489399E-4</v>
@@ -9145,7 +9145,7 @@
         <v>5.0778027585015682E-3</v>
       </c>
       <c r="E30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.7872858113367872E-7</v>
       </c>
       <c r="F30" s="1">
@@ -9181,11 +9181,11 @@
         <v>25</v>
       </c>
       <c r="CY30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2.0361857434010359E-6</v>
       </c>
     </row>
-    <row r="31" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <f>+Inlet!D35</f>
         <v>3.3641283729567801E-4</v>
@@ -9199,7 +9199,7 @@
         <v>5.0778027585015682E-3</v>
       </c>
       <c r="E31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7082380332153329E-6</v>
       </c>
       <c r="F31" s="1">
@@ -9235,11 +9235,11 @@
         <v>26</v>
       </c>
       <c r="CY31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>5.124714099645998E-6</v>
       </c>
     </row>
-    <row r="32" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B32" s="5">
         <f>+Inlet!D36</f>
         <v>2.8889358344335599E-11</v>
@@ -9253,7 +9253,7 @@
         <v>5.0778027585015682E-3</v>
       </c>
       <c r="E32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.4669446349220759E-13</v>
       </c>
       <c r="F32" s="1">
@@ -9289,11 +9289,11 @@
         <v>27</v>
       </c>
       <c r="CY32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4.4008339047662278E-13</v>
       </c>
     </row>
-    <row r="33" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <f>+Inlet!D37</f>
         <v>8.4212847972979201E-5</v>
@@ -9306,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F33" s="1">
@@ -9326,11 +9326,11 @@
         <v>28</v>
       </c>
       <c r="CY33">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:103" x14ac:dyDescent="0.2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <f>+Inlet!D38</f>
         <v>6.2978783674192802E-9</v>
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F34" s="1">
@@ -9363,11 +9363,11 @@
         <v>29</v>
       </c>
       <c r="CY34">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:103" x14ac:dyDescent="0.2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <f>+Inlet!D39</f>
         <v>5.31262659394946E-5</v>
@@ -9381,7 +9381,7 @@
         <v>7.2097323535389914E-3</v>
       </c>
       <c r="E35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.8302615836669078E-7</v>
       </c>
       <c r="F35" s="1">
@@ -9421,11 +9421,11 @@
         <v>30</v>
       </c>
       <c r="CY35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.5321046334667631E-6</v>
       </c>
     </row>
-    <row r="36" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <f>+Inlet!D40</f>
         <v>3.98999016549474E-5</v>
@@ -9439,7 +9439,7 @@
         <v>7.2097323535389914E-3</v>
       </c>
       <c r="E36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8766761186469824E-7</v>
       </c>
       <c r="F36" s="1">
@@ -9483,7 +9483,7 @@
         <v>1.150670447458793E-6</v>
       </c>
     </row>
-    <row r="37" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B37" s="5">
         <f>+Inlet!D41</f>
         <v>2.9005430040026501E-8</v>
@@ -9497,7 +9497,7 @@
         <v>7.2097323535389914E-3</v>
       </c>
       <c r="E37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0912138738789082E-10</v>
       </c>
       <c r="F37" s="1">
@@ -9541,7 +9541,7 @@
         <v>8.3648554955156326E-10</v>
       </c>
     </row>
-    <row r="38" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <f>+Inlet!D42</f>
         <v>1.2093808049619699E-5</v>
@@ -9554,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F38" s="1">
@@ -9578,7 +9578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B39" s="5">
         <f>+Inlet!D43</f>
         <v>3.2000962591801201E-7</v>
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F39" s="1">
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B40" s="5">
         <f>+Inlet!D44</f>
         <v>6.36753582062744E-6</v>
@@ -9629,7 +9629,7 @@
         <v>9.8271963746152571E-3</v>
       </c>
       <c r="E40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.2575024931702768E-8</v>
       </c>
       <c r="F40" s="1">
@@ -9677,7 +9677,7 @@
         <v>3.1287512465851383E-7</v>
       </c>
     </row>
-    <row r="41" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B41" s="5">
         <f>+Inlet!D45</f>
         <v>6.9458670121346895E-7</v>
@@ -9691,7 +9691,7 @@
         <v>9.8271963746152571E-3</v>
       </c>
       <c r="E41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.8258399120209729E-9</v>
       </c>
       <c r="F41" s="1">
@@ -9739,7 +9739,7 @@
         <v>3.4129199560104865E-8</v>
       </c>
     </row>
-    <row r="42" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B42" s="5">
         <f>+Inlet!D46</f>
         <v>1.65554693590926E-7</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F42" s="1">
@@ -9776,7 +9776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B43" s="5">
         <f>+Inlet!D47</f>
         <v>2.8947638471494402E-7</v>
@@ -9836,7 +9836,7 @@
         <v>1.4223706392037147E-8</v>
       </c>
     </row>
-    <row r="44" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B44" s="5">
         <f>+Inlet!D48</f>
         <v>1.15040433650954E-6</v>
@@ -9850,7 +9850,7 @@
         <v>1.3235937670102347E-2</v>
       </c>
       <c r="E44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5226680093455718E-8</v>
       </c>
       <c r="F44" s="1">
@@ -9902,7 +9902,7 @@
         <v>9.136008056073432E-8</v>
       </c>
     </row>
-    <row r="45" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <f>+Inlet!D49</f>
         <v>5.0522337157809797E-6</v>
@@ -9916,7 +9916,7 @@
         <v>1.3235937670102347E-2</v>
       </c>
       <c r="E45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.6871050556866617E-8</v>
       </c>
       <c r="F45" s="1">
@@ -9968,7 +9968,7 @@
         <v>4.0122630334119973E-7</v>
       </c>
     </row>
-    <row r="46" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B46" s="5">
         <f>+Inlet!D50</f>
         <v>1.42872677173312E-7</v>
@@ -9982,7 +9982,7 @@
         <v>1.3235937670102347E-2</v>
       </c>
       <c r="E46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8910538498266118E-9</v>
       </c>
       <c r="F46" s="1">
@@ -10034,7 +10034,7 @@
         <v>1.134632309895967E-8</v>
       </c>
     </row>
-    <row r="47" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B47" s="5">
         <f>+Inlet!D51</f>
         <v>5.4930049786511697E-7</v>
@@ -10047,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F47" s="1">
@@ -10071,7 +10071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B48" s="5">
         <f>+Inlet!D52</f>
         <v>9.8777101473426203E-8</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <f>+Inlet!D53</f>
         <v>1.7767883216190999E-6</v>
@@ -10120,7 +10120,7 @@
         <v>1.779822099938571E-2</v>
       </c>
       <c r="E49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1623671217304354E-8</v>
       </c>
       <c r="F49" s="1">
@@ -10176,7 +10176,7 @@
         <v>2.213656985211305E-7</v>
       </c>
     </row>
-    <row r="50" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B50" s="5">
         <f>+Inlet!D54</f>
         <v>2.06538218262178E-7</v>
@@ -10190,7 +10190,7 @@
         <v>1.779822099938571E-2</v>
       </c>
       <c r="E50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6760128534496055E-9</v>
       </c>
       <c r="F50" s="1">
@@ -10246,7 +10246,7 @@
         <v>2.5732089974147242E-8</v>
       </c>
     </row>
-    <row r="51" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B51" s="5">
         <f>+Inlet!D55</f>
         <v>1.43202293204218E-5</v>
@@ -10260,7 +10260,7 @@
         <v>1.779822099938571E-2</v>
       </c>
       <c r="E51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.5487460620675024E-7</v>
       </c>
       <c r="F51" s="1">
@@ -10316,7 +10316,7 @@
         <v>1.7841222434472515E-6</v>
       </c>
     </row>
-    <row r="52" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B52" s="5">
         <f>+Inlet!D56</f>
         <v>1.73939982511811E-6</v>
@@ -10330,7 +10330,7 @@
         <v>2.3997016793279102E-2</v>
       </c>
       <c r="E52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1740406813586017E-8</v>
       </c>
       <c r="F52" s="1">
@@ -10390,7 +10390,7 @@
         <v>3.3392325450868819E-7</v>
       </c>
     </row>
-    <row r="53" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B53" s="5">
         <f>+Inlet!D57</f>
         <v>6.3342220320428803E-5</v>
@@ -10404,7 +10404,7 @@
         <v>2.3997016793279102E-2</v>
       </c>
       <c r="E53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5200243247529147E-6</v>
       </c>
       <c r="F53" s="1">
@@ -10464,7 +10464,7 @@
         <v>1.2160194598023317E-5</v>
       </c>
     </row>
-    <row r="54" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B54" s="5">
         <f>+Inlet!D58</f>
         <v>1.0679308080105E-5</v>
@@ -10478,7 +10478,7 @@
         <v>3.250089925499041E-2</v>
       </c>
       <c r="E54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.4708711602449766E-7</v>
       </c>
       <c r="F54" s="1">
@@ -10542,7 +10542,7 @@
         <v>3.1237840442204795E-6</v>
       </c>
     </row>
-    <row r="55" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B55" s="5">
         <f>+Inlet!D59</f>
         <v>2.4524703067885402E-4</v>
@@ -10556,7 +10556,7 @@
         <v>3.250089925499041E-2</v>
       </c>
       <c r="E55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.9707490366789767E-6</v>
       </c>
       <c r="F55" s="1">
@@ -10620,7 +10620,7 @@
         <v>7.1736741330110789E-5</v>
       </c>
     </row>
-    <row r="56" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B56" s="5">
         <f>+Inlet!D60</f>
         <v>7.2695341019647397E-5</v>
@@ -10634,7 +10634,7 @@
         <v>4.4248415255681427E-2</v>
       </c>
       <c r="E56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2166536365907297E-6</v>
       </c>
       <c r="F56" s="1">
@@ -10702,7 +10702,7 @@
         <v>3.2166536365907292E-5</v>
       </c>
     </row>
-    <row r="57" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B57" s="5">
         <f>+Inlet!D61</f>
         <v>9.2880678479418603E-4</v>
@@ -10716,7 +10716,7 @@
         <v>4.4248415255681427E-2</v>
       </c>
       <c r="E57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1098228305867476E-5</v>
       </c>
       <c r="F57" s="1">
@@ -10784,7 +10784,7 @@
         <v>4.1098228305867476E-4</v>
       </c>
     </row>
-    <row r="58" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B58" s="5">
         <f>+Inlet!D62</f>
         <v>6.1810605848908699E-5</v>
@@ -10798,7 +10798,7 @@
         <v>6.0565649256238925E-2</v>
       </c>
       <c r="E58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7435994741606343E-6</v>
       </c>
       <c r="F58" s="1">
@@ -10870,7 +10870,7 @@
         <v>4.1179594215766984E-5</v>
       </c>
     </row>
-    <row r="59" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B59" s="5">
         <f>+Inlet!D63</f>
         <v>4.5669906775103099E-3</v>
@@ -10884,7 +10884,7 @@
         <v>6.0565649256238925E-2</v>
       </c>
       <c r="E59">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7660275553060241E-4</v>
       </c>
       <c r="F59" s="1">
@@ -10956,7 +10956,7 @@
         <v>3.0426303108366266E-3</v>
       </c>
     </row>
-    <row r="60" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B60" s="5">
         <f>+Inlet!D64</f>
         <v>3.8067033145851602E-2</v>
@@ -10969,7 +10969,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="E60">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1722527621543001E-3</v>
       </c>
       <c r="F60" s="1">
@@ -11041,7 +11041,7 @@
         <v>3.8067033145851588E-2</v>
       </c>
     </row>
-    <row r="61" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B61" s="5">
         <f>+Inlet!D65</f>
         <v>3.1509682024503501E-2</v>
@@ -11054,7 +11054,7 @@
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="E61">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4238216941925772E-3</v>
       </c>
       <c r="F61" s="1">
@@ -11130,7 +11130,7 @@
         <v>3.1509682024503508E-2</v>
       </c>
     </row>
-    <row r="62" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B62" s="5">
         <f>+Inlet!D66</f>
         <v>2.4954334528562001E-2</v>
@@ -11143,7 +11143,7 @@
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="E62">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7824524663258572E-3</v>
       </c>
       <c r="F62" s="1">
@@ -11153,7 +11153,7 @@
         <v>55</v>
       </c>
       <c r="L62">
-        <f t="shared" si="24"/>
+        <f>+E62</f>
         <v>1.7824524663258572E-3</v>
       </c>
       <c r="N62">
@@ -11223,7 +11223,7 @@
         <v>2.4954334528561998E-2</v>
       </c>
     </row>
-    <row r="63" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B63" s="5">
         <f>+Inlet!D67</f>
         <v>2.2686976780200201E-2</v>
@@ -11236,7 +11236,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="E63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5124651186800135E-3</v>
       </c>
       <c r="F63" s="1">
@@ -11320,7 +11320,7 @@
         <v>2.2686976780200208E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B64" s="5">
         <f>+Inlet!D68</f>
         <v>2.0418279046158099E-2</v>
@@ -11333,7 +11333,7 @@
         <v>6.25E-2</v>
       </c>
       <c r="E64">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2761424403848812E-3</v>
       </c>
       <c r="F64" s="1">
@@ -11421,7 +11421,7 @@
         <v>2.0418279046158099E-2</v>
       </c>
     </row>
-    <row r="65" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B65" s="5">
         <f>+Inlet!D69</f>
         <v>1.81495907482754E-2</v>
@@ -11434,7 +11434,7 @@
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="E65">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0676229851926706E-3</v>
       </c>
       <c r="F65" s="1">
@@ -11526,7 +11526,7 @@
         <v>1.8149590748275404E-2</v>
       </c>
     </row>
-    <row r="66" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B66" s="5">
         <f>+Inlet!D70</f>
         <v>1.7015207469495301E-2</v>
@@ -11539,7 +11539,7 @@
         <v>5.5555555555555552E-2</v>
       </c>
       <c r="E66">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.4528930386084998E-4</v>
       </c>
       <c r="F66" s="1">
@@ -11635,7 +11635,7 @@
         <v>1.7015207469495298E-2</v>
       </c>
     </row>
-    <row r="67" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B67" s="5">
         <f>+Inlet!D71</f>
         <v>1.47465541544741E-2</v>
@@ -11648,7 +11648,7 @@
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="E67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.7613442918284729E-4</v>
       </c>
       <c r="F67" s="1">
@@ -11748,7 +11748,7 @@
         <v>1.4746554154474095E-2</v>
       </c>
     </row>
-    <row r="68" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B68" s="5">
         <f>+Inlet!D72</f>
         <v>1.2477807698799699E-2</v>
@@ -11761,7 +11761,7 @@
         <v>0.05</v>
       </c>
       <c r="E68">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.2389038493998504E-4</v>
       </c>
       <c r="F68" s="1">
@@ -11865,7 +11865,7 @@
         <v>1.2477807698799696E-2</v>
       </c>
     </row>
-    <row r="69" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B69" s="5">
         <f>+Inlet!D73</f>
         <v>1.0209164322309099E-2</v>
@@ -11874,11 +11874,11 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <f t="shared" si="6"/>
+        <f>1/(F69-6)*C69</f>
         <v>4.7619047619047616E-2</v>
       </c>
       <c r="E69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.8615068201471898E-4</v>
       </c>
       <c r="F69" s="1">
@@ -11986,7 +11986,7 @@
         <v>1.0209164322309099E-2</v>
       </c>
     </row>
-    <row r="70" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B70" s="5">
         <f>+Inlet!D74</f>
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>4.5454545454545456E-2</v>
       </c>
       <c r="E70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F70" s="1">
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B71" s="5">
         <f>+Inlet!D75</f>
         <v>0</v>
@@ -12124,7 +12124,7 @@
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="E71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F71" s="1">
@@ -12240,7 +12240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B72" s="5">
         <f>+Inlet!D76</f>
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="E72">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F72" s="1">
@@ -12373,7 +12373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B73" s="5">
         <f>+Inlet!D77</f>
         <v>0</v>
@@ -12386,7 +12386,7 @@
         <v>0.04</v>
       </c>
       <c r="E73">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F73" s="1">
@@ -12510,7 +12510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B74" s="5">
         <f>+Inlet!D78</f>
         <v>0</v>
@@ -12523,7 +12523,7 @@
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="E74">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F74" s="1">
@@ -12651,7 +12651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B75" s="5">
         <f>+Inlet!D79</f>
         <v>0</v>
@@ -12664,7 +12664,7 @@
         <v>3.7037037037037035E-2</v>
       </c>
       <c r="E75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F75" s="1">
@@ -12796,7 +12796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B76" s="5">
         <f>+Inlet!D80</f>
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="E76">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F76" s="1">
@@ -12945,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B77" s="5">
         <f>+Inlet!D81</f>
         <v>0</v>
@@ -12958,7 +12958,7 @@
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E77">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F77" s="1">
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B78" s="5">
         <f>+Inlet!D82</f>
         <v>0</v>
@@ -13111,7 +13111,7 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="E78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F78" s="1">
@@ -13255,7 +13255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B79" s="5">
         <f>+Inlet!D83</f>
         <v>0</v>
@@ -13268,7 +13268,7 @@
         <v>3.2258064516129031E-2</v>
       </c>
       <c r="E79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F79" s="1">
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B80" s="5">
         <f>+Inlet!D84</f>
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>3.125E-2</v>
       </c>
       <c r="E80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F80" s="1">
@@ -13581,7 +13581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B81" s="5">
         <f>+Inlet!D85</f>
         <v>0</v>
@@ -13594,7 +13594,7 @@
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="E81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F81" s="1">
@@ -13750,7 +13750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B82" s="5">
         <f>+Inlet!D86</f>
         <v>0</v>
@@ -13763,7 +13763,7 @@
         <v>2.9411764705882353E-2</v>
       </c>
       <c r="E82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F82" s="1">
@@ -13923,7 +13923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B83" s="5">
         <f>+Inlet!D87</f>
         <v>0</v>
@@ -13936,7 +13936,7 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="E83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F83" s="1">
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B84" s="5">
         <f>+Inlet!D88</f>
         <v>0</v>
@@ -14113,7 +14113,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
       <c r="E84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F84" s="1">
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B85" s="5">
         <f>+Inlet!D89</f>
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>2.7027027027027029E-2</v>
       </c>
       <c r="E85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F85" s="1">
@@ -14466,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B86" s="5">
         <f>+Inlet!D90</f>
         <v>0</v>
@@ -14655,7 +14655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B87" s="5">
         <f>+Inlet!D91</f>
         <v>0</v>
@@ -14848,7 +14848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B88" s="5">
         <f>+Inlet!D92</f>
         <v>0</v>
@@ -15045,7 +15045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B89" s="5">
         <f>+Inlet!D93</f>
         <v>0</v>
@@ -15250,7 +15250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B90" s="5">
         <f>+Inlet!D94</f>
         <v>0</v>
@@ -15463,7 +15463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B91" s="5">
         <f>+Inlet!D95</f>
         <v>0</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B92" s="5">
         <f>+Inlet!D96</f>
         <v>0</v>
@@ -15893,7 +15893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B93" s="5">
         <f>+Inlet!D97</f>
         <v>0</v>
@@ -16114,7 +16114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:103" x14ac:dyDescent="0.25">
       <c r="D94">
         <f t="shared" si="59"/>
         <v>0</v>
@@ -16396,7 +16396,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="95" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:103" x14ac:dyDescent="0.25">
       <c r="G95" t="s">
         <v>0</v>
       </c>
@@ -16680,16 +16680,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:103" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
         <v>91</v>
       </c>
-      <c r="H96">
-        <f t="shared" ref="H96:AM96" si="62">SUM(H2:H93)</f>
+      <c r="H96" s="5">
+        <f>SUM(H2:H93)</f>
         <v>7.1114470114353595E-4</v>
       </c>
       <c r="I96">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="H96:AM96" si="62">SUM(I2:I93)</f>
         <v>1.15915726277396E-3</v>
       </c>
       <c r="J96">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="N96">
         <f t="shared" si="62"/>
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="O96">
         <f t="shared" si="62"/>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="CY96">
         <f>+SUM(CY2:CY93)</f>
-        <v>0.21386968251157829</v>
+        <v>0.21422285439431871</v>
       </c>
     </row>
   </sheetData>
@@ -17069,9 +17069,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6DC9C9-DF88-0449-A30B-C123CD77EA2C}">
   <dimension ref="A1:CY98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>89</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.4</v>
       </c>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B4">
         <f>Primary!CV4</f>
         <v>2.5701200645325E-3</v>
@@ -17467,7 +17467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B5">
         <f>Primary!CV5</f>
         <v>0</v>
@@ -17500,7 +17500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B6">
         <f>Primary!CV6</f>
         <v>3.8202128189215881E-2</v>
@@ -17532,7 +17532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B7">
         <f>Primary!CV7</f>
         <v>1.1449167841188555E-8</v>
@@ -17564,17 +17564,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B8">
         <f>Primary!CV8</f>
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -17584,10 +17584,10 @@
       </c>
       <c r="N8">
         <f>(1-$C8)*$B8</f>
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="CV8">
-        <v>6.7053693992314714E-2</v>
+        <v>6.7760037757795585E-2</v>
       </c>
       <c r="CW8" s="2" t="s">
         <v>8</v>
@@ -17596,7 +17596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B9">
         <f>Primary!CV9</f>
         <v>8.7688471000871231E-5</v>
@@ -17628,7 +17628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B10">
         <f>Primary!CV10</f>
         <v>8.1154749464936498E-23</v>
@@ -17660,7 +17660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B11">
         <f>Primary!CV11</f>
         <v>4.1243721045750262E-2</v>
@@ -17692,7 +17692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B12">
         <f>Primary!CV12</f>
         <v>7.9740251659888401E-4</v>
@@ -17722,7 +17722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B13">
         <f>Primary!CV13</f>
         <v>4.9454120758277598E-20</v>
@@ -17754,7 +17754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B14">
         <f>Primary!CV14</f>
         <v>7.7846204715078602E-5</v>
@@ -17784,7 +17784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B15">
         <f>Primary!CV15</f>
         <v>2.94082363397296E-3</v>
@@ -17816,7 +17816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B16">
         <f>Primary!CV16</f>
         <v>3.3540807671867665E-2</v>
@@ -17848,7 +17848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:103" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:103" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17">
         <f>Primary!CV17</f>
         <v>1.63131923146749E-17</v>
@@ -17881,7 +17881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:103" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:103" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>Primary!CV18</f>
         <v>4.3282018242143298E-19</v>
@@ -17912,7 +17912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:103" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:103" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19">
         <f>Primary!CV19</f>
         <v>2.0961080448768401E-4</v>
@@ -17943,7 +17943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B20">
         <f>Primary!CV20</f>
         <v>2.9972459814883948E-2</v>
@@ -17981,7 +17981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B21">
         <f>Primary!CV21</f>
         <v>1.44797760949513E-3</v>
@@ -18019,7 +18019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B22">
         <f>Primary!CV22</f>
         <v>1.61549255798959E-15</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B23">
         <f>Primary!CV23</f>
         <v>1.1090436396881701E-15</v>
@@ -18094,7 +18094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B24">
         <f>Primary!CV24</f>
         <v>1.9452524184119399E-4</v>
@@ -18129,7 +18129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B25">
         <f>Primary!CV25</f>
         <v>2.9582865180567526E-2</v>
@@ -18179,7 +18179,7 @@
         <v>1.8085054846810647E-4</v>
       </c>
     </row>
-    <row r="26" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B26">
         <f>Primary!CV26</f>
         <v>5.1982099576249085E-4</v>
@@ -18229,7 +18229,7 @@
         <v>3.1778501377424794E-6</v>
       </c>
     </row>
-    <row r="27" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B27">
         <f>Primary!CV27</f>
         <v>6.6700119975318329E-13</v>
@@ -18279,7 +18279,7 @@
         <v>4.0776149324267068E-15</v>
       </c>
     </row>
-    <row r="28" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B28">
         <f>Primary!CV28</f>
         <v>3.6401436079514898E-4</v>
@@ -18316,7 +18316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B29">
         <f>Primary!CV29</f>
         <v>3.55320707761801E-12</v>
@@ -18353,7 +18353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B30">
         <f>Primary!CV30</f>
         <v>2.8933820163736929E-2</v>
@@ -18407,7 +18407,7 @@
         <v>4.40760695524235E-4</v>
       </c>
     </row>
-    <row r="31" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B31">
         <f>Primary!CV31</f>
         <v>3.3128812319603205E-4</v>
@@ -18461,7 +18461,7 @@
         <v>5.0466472374708574E-6</v>
       </c>
     </row>
-    <row r="32" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B32">
         <f>Primary!CV32</f>
         <v>2.8449274953858978E-11</v>
@@ -18515,7 +18515,7 @@
         <v>4.3337942051422406E-13</v>
       </c>
     </row>
-    <row r="33" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>Primary!CV33</f>
         <v>8.4212847972979201E-5</v>
@@ -18552,7 +18552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B34">
         <f>Primary!CV34</f>
         <v>6.2978783674192802E-9</v>
@@ -18589,7 +18589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B35">
         <f>Primary!CV35</f>
         <v>2.8853410545116684E-2</v>
@@ -18647,7 +18647,7 @@
         <v>8.3210147006828347E-4</v>
       </c>
     </row>
-    <row r="36" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B36">
         <f>Primary!CV36</f>
         <v>3.8749231207488604E-5</v>
@@ -18705,7 +18705,7 @@
         <v>1.1174863436455736E-6</v>
       </c>
     </row>
-    <row r="37" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B37">
         <f>Primary!CV37</f>
         <v>2.8168944490474935E-8</v>
@@ -18763,7 +18763,7 @@
         <v>8.1236220183208414E-10</v>
       </c>
     </row>
-    <row r="38" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B38">
         <f>Primary!CV38</f>
         <v>1.2093808049619699E-5</v>
@@ -18800,7 +18800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B39">
         <f>Primary!CV39</f>
         <v>3.2000962591801201E-7</v>
@@ -18837,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B40">
         <f>Primary!CV40</f>
         <v>2.8806019105484783E-2</v>
@@ -18899,7 +18899,7 @@
         <v>1.4154120326025893E-3</v>
       </c>
     </row>
-    <row r="41" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B41">
         <f>Primary!CV41</f>
         <v>6.6045750165336401E-7</v>
@@ -18961,7 +18961,7 @@
         <v>3.2452227829176945E-8</v>
       </c>
     </row>
-    <row r="42" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B42">
         <f>Primary!CV42</f>
         <v>1.65554693590926E-7</v>
@@ -18998,7 +18998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B43">
         <f>Primary!CV43</f>
         <v>2.7525267832290686E-7</v>
@@ -19057,7 +19057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B44">
         <f>Primary!CV44</f>
         <v>1.0590442559488057E-6</v>
@@ -19123,7 +19123,7 @@
         <v>8.410466256970985E-8</v>
       </c>
     </row>
-    <row r="45" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B45">
         <f>Primary!CV45</f>
         <v>2.8794735851316984E-2</v>
@@ -19189,7 +19189,7 @@
         <v>2.2867519737305581E-3</v>
       </c>
     </row>
-    <row r="46" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B46">
         <f>Primary!CV46</f>
         <v>1.3152635407435234E-7</v>
@@ -19255,7 +19255,7 @@
         <v>1.0445247747023636E-8</v>
       </c>
     </row>
-    <row r="47" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B47">
         <f>Primary!CV47</f>
         <v>5.4930049786511697E-7</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B48">
         <f>Primary!CV48</f>
         <v>9.8777101473426203E-8</v>
@@ -19327,7 +19327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B49">
         <f>Primary!CV49</f>
         <v>1.5554226230979695E-6</v>
@@ -19397,7 +19397,7 @@
         <v>1.9378628915339317E-7</v>
       </c>
     </row>
-    <row r="50" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B50">
         <f>Primary!CV50</f>
         <v>1.8080612828803075E-7</v>
@@ -19467,7 +19467,7 @@
         <v>2.2526192005195585E-8</v>
       </c>
     </row>
-    <row r="51" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" ref="A51:A60" si="23">SUM(H51:CV51)</f>
         <v>6.5984810736712363E-2</v>
@@ -19541,7 +19541,7 @@
         <v>3.5818905100905504E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="23"/>
         <v>2.8109531412188437E-6</v>
@@ -19619,7 +19619,7 @@
         <v>2.6981795893979695E-7</v>
       </c>
     </row>
-    <row r="53" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="23"/>
         <v>6.3519624329199234E-2</v>
@@ -19697,7 +19697,7 @@
         <v>5.464403488277818E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="23"/>
         <v>1.5111048071769042E-5</v>
@@ -19779,7 +19779,7 @@
         <v>2.2100519295804728E-6</v>
       </c>
     </row>
-    <row r="55" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="23"/>
         <v>5.4858887473395027E-2</v>
@@ -19861,7 +19861,7 @@
         <v>7.3518112673207157E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="23"/>
         <v>8.1057609307480223E-5</v>
@@ -19947,7 +19947,7 @@
         <v>1.793335378135086E-5</v>
       </c>
     </row>
-    <row r="57" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="23"/>
         <v>4.2668765392288789E-2</v>
@@ -20033,7 +20033,7 @@
         <v>8.797444176119721E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="23"/>
         <v>4.1262023266283444E-5</v>
@@ -20123,7 +20123,7 @@
         <v>1.374483675811671E-5</v>
       </c>
     </row>
-    <row r="59" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="23"/>
         <v>3.5090510582676614E-2</v>
@@ -20213,7 +20213,7 @@
         <v>1.1114053360355635E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="23"/>
         <v>2.4656691570156819E-2</v>
@@ -20302,7 +20302,7 @@
         <v>1.1862925569831919E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B61">
         <f>Primary!CV61</f>
         <v>9.0743180107670258E-3</v>
@@ -20391,7 +20391,7 @@
         <v>9.0743180107670275E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B62">
         <f>Primary!CV62</f>
         <v>6.7305525851894732E-3</v>
@@ -20484,7 +20484,7 @@
         <v>6.7305525851894732E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B63">
         <f>Primary!CV63</f>
         <v>4.7176402961359529E-3</v>
@@ -20581,7 +20581,7 @@
         <v>4.7176402961359529E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:103" x14ac:dyDescent="0.25">
       <c r="B64">
         <f>Primary!CV64</f>
         <v>2.9962165630922554E-3</v>
@@ -20682,7 +20682,7 @@
         <v>2.9962165630922559E-3</v>
       </c>
     </row>
-    <row r="65" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B65">
         <f>Primary!CV65</f>
         <v>1.596191748969423E-3</v>
@@ -20787,7 +20787,7 @@
         <v>1.5961917489694234E-3</v>
       </c>
     </row>
-    <row r="66" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B66">
         <f>Primary!CV66</f>
         <v>4.8615068201471898E-4</v>
@@ -20896,7 +20896,7 @@
         <v>4.8615068201471909E-4</v>
       </c>
     </row>
-    <row r="67" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B67">
         <f>Primary!CV67</f>
         <v>0</v>
@@ -21009,7 +21009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B68">
         <f>Primary!CV68</f>
         <v>0</v>
@@ -21126,7 +21126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B69">
         <f>Primary!CV69</f>
         <v>0</v>
@@ -21247,7 +21247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B70">
         <f>Primary!CV70</f>
         <v>0</v>
@@ -21372,7 +21372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B71">
         <f>Primary!CV71</f>
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B72">
         <f>Primary!CV72</f>
         <v>0</v>
@@ -21634,7 +21634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B73">
         <f>Primary!CV73</f>
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B74">
         <f>Primary!CV74</f>
         <v>0</v>
@@ -21912,7 +21912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B75">
         <f>Primary!CV75</f>
         <v>0</v>
@@ -22057,7 +22057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B76">
         <f>Primary!CV76</f>
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B77">
         <f>Primary!CV77</f>
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B78">
         <f>Primary!CV78</f>
         <v>0</v>
@@ -22516,7 +22516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B79">
         <f>Primary!CV79</f>
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B80">
         <f>Primary!CV80</f>
         <v>0</v>
@@ -22842,7 +22842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B81">
         <f>Primary!CV81</f>
         <v>0</v>
@@ -23011,7 +23011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B82">
         <f>Primary!CV82</f>
         <v>0</v>
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B83">
         <f>Primary!CV83</f>
         <v>0</v>
@@ -23361,7 +23361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B84">
         <f>Primary!CV84</f>
         <v>0</v>
@@ -23542,7 +23542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B85">
         <f>Primary!CV85</f>
         <v>0</v>
@@ -23727,7 +23727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B86">
         <f>Primary!CV86</f>
         <v>0</v>
@@ -23916,7 +23916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B87">
         <f>Primary!CV87</f>
         <v>0</v>
@@ -24109,7 +24109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B88">
         <f>Primary!CV88</f>
         <v>0</v>
@@ -24306,7 +24306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B89">
         <f>Primary!CV89</f>
         <v>0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B90">
         <f>Primary!CV90</f>
         <v>0</v>
@@ -24724,7 +24724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B91">
         <f>Primary!CV91</f>
         <v>0</v>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B92">
         <f>Primary!CV92</f>
         <v>0</v>
@@ -25154,7 +25154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B93">
         <f>Primary!CV93</f>
         <v>0</v>
@@ -25375,7 +25375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:103" x14ac:dyDescent="0.25">
       <c r="B94">
         <f>Primary!CV94</f>
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="95" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:103" x14ac:dyDescent="0.25">
       <c r="G95" t="s">
         <v>0</v>
       </c>
@@ -25943,7 +25943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:103" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:103" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
         <v>91</v>
       </c>
@@ -25973,7 +25973,7 @@
       </c>
       <c r="N96">
         <f t="shared" si="51"/>
-        <v>6.7053693992314714E-2</v>
+        <v>6.7760037757795585E-2</v>
       </c>
       <c r="O96">
         <f t="shared" si="51"/>
@@ -26323,10 +26323,10 @@
         <v>7.8973319150124788E-2</v>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H98">
         <f>H96/SUM($H$96:$CU$96)</f>
-        <v>1.2128295319597418E-3</v>
+        <v>1.2113702647960803E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26338,9 +26338,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148F672D-9C24-DD48-B0E6-043C04345249}">
   <dimension ref="B2:K73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>93</v>
       </c>
@@ -26353,13 +26353,13 @@
       </c>
       <c r="F2" s="10">
         <f>+D2/SUM($D$2:$D$73)</f>
-        <v>1.3943353279691989E-2</v>
+        <v>1.3942561137519472E-2</v>
       </c>
       <c r="K2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>94</v>
       </c>
@@ -26372,13 +26372,13 @@
       </c>
       <c r="F3" s="10">
         <f t="shared" ref="F3:F66" si="0">+D3/SUM($D$2:$D$73)</f>
-        <v>9.7235495029578394E-4</v>
+        <v>9.7229970939731903E-4</v>
       </c>
       <c r="K3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -26387,17 +26387,17 @@
       </c>
       <c r="D4">
         <f>+Inlet!D4-Primary!CY96-Secondary!CY96</f>
-        <v>5.5370884759038166</v>
+        <v>5.5367353040210769</v>
       </c>
       <c r="F4" s="10">
         <f t="shared" si="0"/>
-        <v>0.89075018267273498</v>
+        <v>0.89064276640583417</v>
       </c>
       <c r="K4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -26410,13 +26410,13 @@
       </c>
       <c r="F5" s="10">
         <f t="shared" si="0"/>
-        <v>7.8367365136260722E-6</v>
+        <v>7.8362912972306461E-6</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -26429,17 +26429,17 @@
       </c>
       <c r="F6" s="10">
         <f t="shared" si="0"/>
-        <v>1.1440168875881183E-4</v>
+        <v>1.143951894325411E-4</v>
       </c>
       <c r="G6" s="9">
         <f>+D6/SUM($D$6:$D$73)</f>
-        <v>1.2128295319597418E-3</v>
+        <v>1.2113702647960803E-3</v>
       </c>
       <c r="K6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -26452,17 +26452,17 @@
       </c>
       <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v>1.8647336918231104E-4</v>
+        <v>1.8646277535908806E-4</v>
       </c>
       <c r="G7" s="9">
         <f t="shared" ref="G7:G70" si="1">+D7/SUM($D$6:$D$73)</f>
-        <v>1.9768974699765378E-3</v>
+        <v>1.9745188821471329E-3</v>
       </c>
       <c r="K7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -26475,17 +26475,17 @@
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>4.1345463901035077E-4</v>
+        <v>4.1343115005117338E-4</v>
       </c>
       <c r="G8" s="9">
         <f t="shared" si="1"/>
-        <v>4.3832394587696444E-3</v>
+        <v>4.3779655787691196E-3</v>
       </c>
       <c r="K8" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -26508,7 +26508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -26521,17 +26521,17 @@
       </c>
       <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>7.4016807781995013E-3</v>
+        <v>7.4012602779529469E-3</v>
       </c>
       <c r="G10" s="9">
         <f t="shared" si="1"/>
-        <v>7.846892061938783E-2</v>
+        <v>7.8374507417688477E-2</v>
       </c>
       <c r="K10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -26544,17 +26544,17 @@
       </c>
       <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v>2.6722572267468677E-9</v>
+        <v>2.6721054119285342E-9</v>
       </c>
       <c r="G11" s="9">
         <f t="shared" si="1"/>
-        <v>2.8329935657018895E-8</v>
+        <v>2.829584929635275E-8</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -26563,21 +26563,21 @@
       </c>
       <c r="D12" s="5">
         <f>+Secondary!CV8</f>
-        <v>6.7053693992314714E-2</v>
+        <v>6.7760037757795585E-2</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" si="0"/>
-        <v>1.0786912730843914E-2</v>
+        <v>1.0899922818513178E-2</v>
       </c>
       <c r="G12" s="9">
         <f t="shared" si="1"/>
-        <v>0.11435745801114588</v>
+        <v>0.11542305630522566</v>
       </c>
       <c r="K12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>9</v>
       </c>
@@ -26590,17 +26590,17 @@
       </c>
       <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>1.6333138633286597E-5</v>
+        <v>1.6332210723933554E-5</v>
       </c>
       <c r="G13" s="9">
         <f t="shared" si="1"/>
-        <v>1.7315577330161342E-4</v>
+        <v>1.729474336071065E-4</v>
       </c>
       <c r="K13" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>10</v>
       </c>
@@ -26613,17 +26613,17 @@
       </c>
       <c r="F14" s="10">
         <f t="shared" si="0"/>
-        <v>1.3055346365736477E-23</v>
+        <v>1.3054604672527847E-23</v>
       </c>
       <c r="G14" s="9">
         <f t="shared" si="1"/>
-        <v>1.3840625775822629E-22</v>
+        <v>1.382397284135248E-22</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>11</v>
       </c>
@@ -26636,17 +26636,17 @@
       </c>
       <c r="F15" s="10">
         <f t="shared" si="0"/>
-        <v>9.1322934715029509E-3</v>
+        <v>9.1317746526330956E-3</v>
       </c>
       <c r="G15" s="9">
         <f t="shared" si="1"/>
-        <v>9.6816011519836959E-2</v>
+        <v>9.6699523239493643E-2</v>
       </c>
       <c r="K15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>96</v>
       </c>
@@ -26659,17 +26659,17 @@
       </c>
       <c r="F16" s="10">
         <f t="shared" si="0"/>
-        <v>1.2827796420721176E-4</v>
+        <v>1.2827067654955763E-4</v>
       </c>
       <c r="G16" s="9">
         <f t="shared" si="1"/>
-        <v>1.3599388695929332E-3</v>
+        <v>1.3583026016058097E-3</v>
       </c>
       <c r="K16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -26682,17 +26682,17 @@
       </c>
       <c r="F17" s="10">
         <f t="shared" si="0"/>
-        <v>7.9556733274276951E-21</v>
+        <v>7.955221354058951E-21</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>8.4342072768445254E-20</v>
+        <v>8.4240593035256978E-20</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>98</v>
       </c>
@@ -26705,17 +26705,17 @@
       </c>
       <c r="F18" s="10">
         <f t="shared" si="0"/>
-        <v>1.2523101513023377E-5</v>
+        <v>1.2522390057418676E-5</v>
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>1.3276366381920725E-4</v>
+        <v>1.3260392360012988E-4</v>
       </c>
       <c r="K18" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -26728,17 +26728,17 @@
       </c>
       <c r="F19" s="10">
         <f t="shared" si="0"/>
-        <v>4.7308963917939279E-4</v>
+        <v>4.7306276226915053E-4</v>
       </c>
       <c r="G19" s="9">
         <f t="shared" si="1"/>
-        <v>5.0154599279615148E-3</v>
+        <v>5.0094253651555547E-3</v>
       </c>
       <c r="K19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>14</v>
       </c>
@@ -26751,17 +26751,17 @@
       </c>
       <c r="F20" s="10">
         <f t="shared" si="0"/>
-        <v>7.8544195765865039E-3</v>
+        <v>7.8539733555905607E-3</v>
       </c>
       <c r="G20" s="9">
         <f t="shared" si="1"/>
-        <v>8.3268631103604163E-2</v>
+        <v>8.3168442927170017E-2</v>
       </c>
       <c r="K20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>15</v>
       </c>
@@ -26774,17 +26774,17 @@
       </c>
       <c r="F21" s="10">
         <f t="shared" si="0"/>
-        <v>2.6242995930998262E-18</v>
+        <v>2.6241505028243876E-18</v>
       </c>
       <c r="G21" s="9">
         <f t="shared" si="1"/>
-        <v>2.7821512791927599E-17</v>
+        <v>2.7788038161741899E-17</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -26797,17 +26797,17 @@
       </c>
       <c r="F22" s="10">
         <f t="shared" si="0"/>
-        <v>6.9627685783620647E-20</v>
+        <v>6.9623730133557313E-20</v>
       </c>
       <c r="G22" s="9">
         <f t="shared" si="1"/>
-        <v>7.3815792823149274E-19</v>
+        <v>7.3726978229022094E-19</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>100</v>
       </c>
@@ -26820,17 +26820,17 @@
       </c>
       <c r="F23" s="10">
         <f t="shared" si="0"/>
-        <v>3.3720043159885885E-5</v>
+        <v>3.3718127475207302E-5</v>
       </c>
       <c r="G23" s="9">
         <f t="shared" si="1"/>
-        <v>3.5748304598446419E-4</v>
+        <v>3.5705292513332705E-4</v>
       </c>
       <c r="K23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -26843,17 +26843,17 @@
       </c>
       <c r="F24" s="10">
         <f t="shared" si="0"/>
-        <v>7.2229646443713316E-3</v>
+        <v>7.2225542972481809E-3</v>
       </c>
       <c r="G24" s="9">
         <f t="shared" si="1"/>
-        <v>7.6574261481956354E-2</v>
+        <v>7.6482127919557288E-2</v>
       </c>
       <c r="K24" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>17</v>
       </c>
@@ -26866,17 +26866,17 @@
       </c>
       <c r="F25" s="10">
         <f t="shared" si="0"/>
-        <v>2.329358336563849E-4</v>
+        <v>2.3292260023300186E-4</v>
       </c>
       <c r="G25" s="9">
         <f t="shared" si="1"/>
-        <v>2.4694692987070523E-3</v>
+        <v>2.466498052242225E-3</v>
       </c>
       <c r="K25" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>18</v>
       </c>
@@ -26889,17 +26889,17 @@
       </c>
       <c r="F26" s="10">
         <f t="shared" si="0"/>
-        <v>2.5988392589316245E-16</v>
+        <v>2.5986916150947871E-16</v>
       </c>
       <c r="G26" s="9">
         <f t="shared" si="1"/>
-        <v>2.7551595052882155E-15</v>
+        <v>2.7518445185643841E-15</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>19</v>
       </c>
@@ -26912,17 +26912,17 @@
       </c>
       <c r="F27" s="10">
         <f t="shared" si="0"/>
-        <v>1.7841160186320141E-16</v>
+        <v>1.7840146604070111E-16</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" si="1"/>
-        <v>1.8914306417287689E-15</v>
+        <v>1.8891548869296933E-15</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>101</v>
       </c>
@@ -26935,17 +26935,17 @@
       </c>
       <c r="F28" s="10">
         <f t="shared" si="0"/>
-        <v>3.12932320764873E-5</v>
+        <v>3.1291454262474786E-5</v>
       </c>
       <c r="G28" s="9">
         <f t="shared" si="1"/>
-        <v>3.3175520767747671E-4</v>
+        <v>3.3135604236348966E-4</v>
       </c>
       <c r="K28" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>20</v>
       </c>
@@ -26958,17 +26958,17 @@
       </c>
       <c r="F29" s="10">
         <f t="shared" si="0"/>
-        <v>7.0521468387896007E-3</v>
+        <v>7.0517461960743428E-3</v>
       </c>
       <c r="G29" s="9">
         <f t="shared" si="1"/>
-        <v>7.4763336473402914E-2</v>
+        <v>7.4673381802044331E-2</v>
       </c>
       <c r="K29" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>21</v>
       </c>
@@ -26981,17 +26981,17 @@
       </c>
       <c r="F30" s="10">
         <f t="shared" si="0"/>
-        <v>8.3112267095703722E-5</v>
+        <v>8.3107545366970377E-5</v>
       </c>
       <c r="G30" s="9">
         <f t="shared" si="1"/>
-        <v>8.811147203806565E-4</v>
+        <v>8.8005456992670719E-4</v>
       </c>
       <c r="K30" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>22</v>
       </c>
@@ -27004,17 +27004,17 @@
       </c>
       <c r="F31" s="10">
         <f t="shared" si="0"/>
-        <v>1.0664436857869898E-13</v>
+        <v>1.066383099570663E-13</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" si="1"/>
-        <v>1.1305903001321133E-12</v>
+        <v>1.1292299825795953E-12</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>23</v>
       </c>
@@ -27027,17 +27027,17 @@
       </c>
       <c r="F32" s="10">
         <f t="shared" si="0"/>
-        <v>5.8558908672820382E-5</v>
+        <v>5.8555581856077972E-5</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="1"/>
-        <v>6.2081228492581601E-4</v>
+        <v>6.200653283599364E-4</v>
       </c>
       <c r="K32" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>24</v>
       </c>
@@ -27050,17 +27050,17 @@
       </c>
       <c r="F33" s="10">
         <f t="shared" si="0"/>
-        <v>5.7160362656940788E-13</v>
+        <v>5.7157115293630933E-13</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="1"/>
-        <v>6.0598559898904252E-12</v>
+        <v>6.0525648177763393E-12</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>25</v>
       </c>
@@ -27073,17 +27073,17 @@
       </c>
       <c r="F34" s="10">
         <f t="shared" si="0"/>
-        <v>6.7990688964432323E-3</v>
+        <v>6.7986826314538375E-3</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="1"/>
-        <v>7.2080330604386497E-2</v>
+        <v>7.1993604105051595E-2</v>
       </c>
       <c r="K34" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>26</v>
       </c>
@@ -27096,17 +27096,17 @@
       </c>
       <c r="F35" s="10">
         <f t="shared" si="0"/>
-        <v>5.2482393151226754E-5</v>
+        <v>5.2479411550165973E-5</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="1"/>
-        <v>5.5639210410542714E-4</v>
+        <v>5.5572265740558497E-4</v>
       </c>
       <c r="K35" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>27</v>
       </c>
@@ -27119,17 +27119,17 @@
       </c>
       <c r="F36" s="10">
         <f t="shared" si="0"/>
-        <v>4.5069108381898629E-12</v>
+        <v>4.5066547940324003E-12</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="1"/>
-        <v>4.7780016377118987E-11</v>
+        <v>4.7722527828942167E-11</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>28</v>
       </c>
@@ -27142,17 +27142,17 @@
       </c>
       <c r="F37" s="10">
         <f t="shared" si="0"/>
-        <v>1.3547301987634974E-5</v>
+        <v>1.3546532345712192E-5</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="1"/>
-        <v>1.4362172540669801E-4</v>
+        <v>1.4344892085143974E-4</v>
       </c>
       <c r="K37" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>29</v>
       </c>
@@ -27165,17 +27165,17 @@
       </c>
       <c r="F38" s="10">
         <f t="shared" si="0"/>
-        <v>1.0131382820849181E-9</v>
+        <v>1.013080724226078E-9</v>
       </c>
       <c r="G38" s="9">
         <f t="shared" si="1"/>
-        <v>1.0740785750655293E-8</v>
+        <v>1.0727862519859181E-8</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>30</v>
       </c>
@@ -27188,17 +27188,17 @@
       </c>
       <c r="F39" s="10">
         <f t="shared" si="0"/>
-        <v>6.5795426176161916E-3</v>
+        <v>6.5791688242338728E-3</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="1"/>
-        <v>6.9753022704553108E-2</v>
+        <v>6.9669096404181438E-2</v>
       </c>
       <c r="K39" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>31</v>
       </c>
@@ -27211,17 +27211,17 @@
       </c>
       <c r="F40" s="10">
         <f t="shared" si="0"/>
-        <v>6.0538103657970535E-6</v>
+        <v>6.05346644002834E-6</v>
       </c>
       <c r="G40" s="9">
         <f t="shared" si="1"/>
-        <v>6.4179472105538606E-5</v>
+        <v>6.4102251858375413E-5</v>
       </c>
       <c r="K40" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>32</v>
       </c>
@@ -27234,17 +27234,17 @@
       </c>
       <c r="F41" s="10">
         <f>+D41/SUM($D$2:$D$73)</f>
-        <v>4.4008472642172769E-9</v>
+        <v>4.4005972456856615E-9</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="1"/>
-        <v>4.6655583371148695E-8</v>
+        <v>4.6599447732115418E-8</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>33</v>
       </c>
@@ -27257,17 +27257,17 @@
       </c>
       <c r="F42" s="10">
         <f t="shared" si="0"/>
-        <v>1.945528191627702E-6</v>
+        <v>1.9454176633424684E-6</v>
       </c>
       <c r="G42" s="9">
         <f t="shared" si="1"/>
-        <v>2.0625517609630213E-5</v>
+        <v>2.0600701145495619E-5</v>
       </c>
       <c r="K42" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>34</v>
       </c>
@@ -27280,17 +27280,17 @@
       </c>
       <c r="F43" s="10">
         <f t="shared" si="0"/>
-        <v>5.1479876831293436E-8</v>
+        <v>5.1476952184642379E-8</v>
       </c>
       <c r="G43" s="9">
         <f t="shared" si="1"/>
-        <v>5.4576392708917588E-7</v>
+        <v>5.4510726813016681E-7</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>35</v>
       </c>
@@ -27303,17 +27303,17 @@
       </c>
       <c r="F44" s="10">
         <f t="shared" si="0"/>
-        <v>6.2858723140638137E-3</v>
+        <v>6.2855152045184172E-3</v>
       </c>
       <c r="G44" s="9">
         <f t="shared" si="1"/>
-        <v>6.6639676908069212E-2</v>
+        <v>6.6559496561411732E-2</v>
       </c>
       <c r="K44" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>36</v>
       </c>
@@ -27326,17 +27326,17 @@
       </c>
       <c r="F45" s="10">
         <f t="shared" si="0"/>
-        <v>1.0102706771125335E-7</v>
+        <v>1.0102132821665013E-7</v>
       </c>
       <c r="G45" s="9">
         <f t="shared" si="1"/>
-        <v>1.071038483582409E-6</v>
+        <v>1.0697498183174857E-6</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>37</v>
       </c>
@@ -27349,17 +27349,17 @@
       </c>
       <c r="F46" s="10">
         <f t="shared" si="0"/>
-        <v>2.6632746469592015E-8</v>
+        <v>2.6631233424542856E-8</v>
       </c>
       <c r="G46" s="9">
         <f t="shared" si="1"/>
-        <v>2.8234706835155657E-7</v>
+        <v>2.820073505307547E-7</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>102</v>
       </c>
@@ -27372,17 +27372,17 @@
       </c>
       <c r="F47" s="10">
         <f t="shared" si="0"/>
-        <v>4.427983669834136E-8</v>
+        <v>4.4277321096438625E-8</v>
       </c>
       <c r="G47" s="9">
         <f t="shared" si="1"/>
-        <v>4.6943269982075839E-7</v>
+        <v>4.6886788200725207E-7</v>
       </c>
       <c r="K47" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>38</v>
       </c>
@@ -27395,17 +27395,17 @@
       </c>
       <c r="F48" s="10">
         <f t="shared" si="0"/>
-        <v>1.5683831397611152E-7</v>
+        <v>1.568294037634622E-7</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" si="1"/>
-        <v>1.6627214248037114E-6</v>
+        <v>1.6607208511751886E-6</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>39</v>
       </c>
@@ -27418,17 +27418,17 @@
       </c>
       <c r="F49" s="10">
         <f t="shared" si="0"/>
-        <v>5.9025484595868916E-3</v>
+        <v>5.9022131272269945E-3</v>
       </c>
       <c r="G49" s="9">
         <f t="shared" si="1"/>
-        <v>6.2575868969058868E-2</v>
+        <v>6.2500578164854437E-2</v>
       </c>
       <c r="K49" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>40</v>
       </c>
@@ -27441,17 +27441,17 @@
       </c>
       <c r="F50" s="10">
         <f t="shared" si="0"/>
-        <v>1.9478290449689825E-8</v>
+        <v>1.9477183859689256E-8</v>
       </c>
       <c r="G50" s="9">
         <f t="shared" si="1"/>
-        <v>2.064991010690267E-7</v>
+        <v>2.0625064293902987E-7</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>41</v>
       </c>
@@ -27464,17 +27464,17 @@
       </c>
       <c r="F51" s="10">
         <f t="shared" si="0"/>
-        <v>8.8365848034550451E-8</v>
+        <v>8.836082784224561E-8</v>
       </c>
       <c r="G51" s="9">
         <f t="shared" si="1"/>
-        <v>9.3681056001644435E-7</v>
+        <v>9.3568339675666259E-7</v>
       </c>
       <c r="K51" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>103</v>
       </c>
@@ -27487,17 +27487,17 @@
       </c>
       <c r="F52" s="10">
         <f t="shared" si="0"/>
-        <v>1.589025018549587E-8</v>
+        <v>1.5889347437279481E-8</v>
       </c>
       <c r="G52" s="9">
         <f t="shared" si="1"/>
-        <v>1.6846049131170463E-7</v>
+        <v>1.6825780094437142E-7</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>42</v>
       </c>
@@ -27510,17 +27510,17 @@
       </c>
       <c r="F53" s="10">
         <f t="shared" si="0"/>
-        <v>2.1904613200116638E-7</v>
+        <v>2.1903368767192909E-7</v>
       </c>
       <c r="G53" s="9">
         <f t="shared" si="1"/>
-        <v>2.3222176231389194E-6</v>
+        <v>2.3194235487574627E-6</v>
       </c>
       <c r="K53" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>43</v>
       </c>
@@ -27533,17 +27533,17 @@
       </c>
       <c r="F54" s="10">
         <f t="shared" si="0"/>
-        <v>2.546245789116651E-8</v>
+        <v>2.5461011331913016E-8</v>
       </c>
       <c r="G54" s="9">
         <f t="shared" si="1"/>
-        <v>2.6994025369498266E-7</v>
+        <v>2.6961546365814127E-7</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>44</v>
       </c>
@@ -27556,17 +27556,17 @@
       </c>
       <c r="F55" s="10">
         <f t="shared" si="0"/>
-        <v>5.4137396307361611E-3</v>
+        <v>5.4134320683165262E-3</v>
       </c>
       <c r="G55" s="9">
         <f t="shared" si="1"/>
-        <v>5.7393762047869237E-2</v>
+        <v>5.7324706314851155E-2</v>
       </c>
       <c r="K55" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>45</v>
       </c>
@@ -27579,17 +27579,17 @@
       </c>
       <c r="F56" s="10">
         <f t="shared" si="0"/>
-        <v>1.8269314644344055E-7</v>
+        <v>1.8268276738016757E-7</v>
       </c>
       <c r="G56" s="9">
         <f t="shared" si="1"/>
-        <v>1.9368214376659157E-6</v>
+        <v>1.9344910690103185E-6</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>104</v>
       </c>
@@ -27602,17 +27602,17 @@
       </c>
       <c r="F57" s="10">
         <f t="shared" si="0"/>
-        <v>4.760337424732277E-3</v>
+        <v>4.7600669830419676E-3</v>
       </c>
       <c r="G57" s="9">
         <f t="shared" si="1"/>
-        <v>5.0466718397666879E-2</v>
+        <v>5.0405997230285285E-2</v>
       </c>
       <c r="K57" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>105</v>
       </c>
@@ -27625,17 +27625,17 @@
       </c>
       <c r="F58" s="10">
         <f t="shared" si="0"/>
-        <v>8.5992490022206581E-7</v>
+        <v>8.5987604663821132E-7</v>
       </c>
       <c r="G58" s="9">
         <f t="shared" si="1"/>
-        <v>9.1164940445559864E-6</v>
+        <v>9.105525149046458E-6</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>48</v>
       </c>
@@ -27648,17 +27648,17 @@
       </c>
       <c r="F59" s="10">
         <f t="shared" si="0"/>
-        <v>3.5991996865159708E-3</v>
+        <v>3.5989952107487858E-3</v>
       </c>
       <c r="G59" s="9">
         <f t="shared" si="1"/>
-        <v>3.8156916375857101E-2</v>
+        <v>3.8111006267580058E-2</v>
       </c>
       <c r="K59" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>49</v>
       </c>
@@ -27671,17 +27671,17 @@
       </c>
       <c r="F60" s="10">
         <f t="shared" si="0"/>
-        <v>3.6349251198967388E-6</v>
+        <v>3.6347186145157415E-6</v>
       </c>
       <c r="G60" s="9">
         <f t="shared" si="1"/>
-        <v>3.8535659566769293E-5</v>
+        <v>3.8489293757598267E-5</v>
       </c>
       <c r="K60" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>50</v>
       </c>
@@ -27694,17 +27694,17 @@
       </c>
       <c r="F61" s="10">
         <f t="shared" si="0"/>
-        <v>2.2504683299596948E-3</v>
+        <v>2.2503404775818404E-3</v>
       </c>
       <c r="G61" s="9">
         <f t="shared" si="1"/>
-        <v>2.385834056234596E-2</v>
+        <v>2.3829634390501817E-2</v>
       </c>
       <c r="K61" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>51</v>
       </c>
@@ -27717,17 +27717,17 @@
       </c>
       <c r="F62" s="10">
         <f t="shared" si="0"/>
-        <v>1.1077774094703622E-6</v>
+        <v>1.1077144750250964E-6</v>
       </c>
       <c r="G62" s="9">
         <f t="shared" si="1"/>
-        <v>1.1744102483277611E-5</v>
+        <v>1.1729972069506412E-5</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>52</v>
       </c>
@@ -27740,17 +27740,17 @@
       </c>
       <c r="F63" s="10">
         <f t="shared" si="0"/>
-        <v>1.1734249587544805E-3</v>
+        <v>1.1733582947764927E-3</v>
       </c>
       <c r="G63" s="9">
         <f t="shared" si="1"/>
-        <v>1.2440064993415195E-2</v>
+        <v>1.2425097202905203E-2</v>
       </c>
       <c r="K63" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>53</v>
       </c>
@@ -27763,17 +27763,17 @@
       </c>
       <c r="F64" s="10">
         <f t="shared" si="0"/>
-        <v>1.4974409152193437E-4</v>
+        <v>1.4973558434237718E-4</v>
       </c>
       <c r="G64" s="9">
         <f t="shared" si="1"/>
-        <v>1.5875120236832649E-3</v>
+        <v>1.5856019414276525E-3</v>
       </c>
       <c r="K64" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>54</v>
       </c>
@@ -27786,17 +27786,17 @@
       </c>
       <c r="F65" s="10">
         <f t="shared" si="0"/>
-        <v>6.9023999395742005E-5</v>
+        <v>6.9020078041980091E-5</v>
       </c>
       <c r="G65" s="9">
         <f t="shared" si="1"/>
-        <v>7.3175794683956658E-4</v>
+        <v>7.3087750130667629E-4</v>
       </c>
       <c r="K65" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>55</v>
       </c>
@@ -27809,17 +27809,17 @@
       </c>
       <c r="F66" s="10">
         <f t="shared" si="0"/>
-        <v>2.3794308848553445E-5</v>
+        <v>2.3792957059272435E-5</v>
       </c>
       <c r="G66" s="9">
         <f t="shared" si="1"/>
-        <v>2.5225537120293412E-4</v>
+        <v>2.5195185948067347E-4</v>
       </c>
       <c r="K66" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>56</v>
       </c>
@@ -27832,17 +27832,17 @@
       </c>
       <c r="F67" s="10">
         <f t="shared" ref="F67:F73" si="2">+D67/SUM($D$2:$D$73)</f>
-        <v>4.3448306281016999E-6</v>
+        <v>4.3445837919566272E-6</v>
       </c>
       <c r="G67" s="9">
         <f t="shared" si="1"/>
-        <v>4.6061722989373683E-5</v>
+        <v>4.6006301878583735E-5</v>
       </c>
       <c r="K67" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>57</v>
       </c>
@@ -27865,7 +27865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>58</v>
       </c>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>59</v>
       </c>
@@ -27911,7 +27911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>60</v>
       </c>
@@ -27934,7 +27934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>61</v>
       </c>
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>62</v>
       </c>
@@ -27988,21 +27988,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0CC36FF-BC1F-E248-8EC8-249FDB9D2F44}">
   <dimension ref="C3:AH95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>118</v>
       </c>
@@ -28019,7 +28019,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>1</v>
       </c>
@@ -28051,7 +28051,7 @@
         <v>7.1114470114353595E-4</v>
       </c>
     </row>
-    <row r="5" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>2</v>
       </c>
@@ -28083,7 +28083,7 @@
         <v>1.15915726277396E-3</v>
       </c>
     </row>
-    <row r="6" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>4</v>
       </c>
@@ -28115,7 +28115,7 @@
         <v>5.1402401290649999E-3</v>
       </c>
     </row>
-    <row r="7" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>5</v>
       </c>
@@ -28159,7 +28159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>6</v>
       </c>
@@ -28215,7 +28215,7 @@
         <v>0.13803116340536808</v>
       </c>
     </row>
-    <row r="9" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>7</v>
       </c>
@@ -28271,7 +28271,7 @@
         <v>4.9833920832235423E-8</v>
       </c>
     </row>
-    <row r="10" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>8</v>
       </c>
@@ -28284,11 +28284,11 @@
       </c>
       <c r="F10" s="5">
         <f>+Secondary!B8</f>
-        <v>5.1451006160106345E-2</v>
+        <v>5.2157349925587217E-2</v>
       </c>
       <c r="G10" s="5">
         <f>+Outlet!D12</f>
-        <v>6.7053693992314714E-2</v>
+        <v>6.7760037757795585E-2</v>
       </c>
       <c r="J10" s="7">
         <v>3</v>
@@ -28320,14 +28320,14 @@
       </c>
       <c r="AG10">
         <f>+Tabella4[[#This Row],[Primary]]*Tabella4[[#This Row],[NC]]</f>
-        <v>0.20580402464042538</v>
+        <v>0.20862939970234887</v>
       </c>
       <c r="AH10">
         <f>+Tabella4[[#This Row],[Secondary]]*Tabella4[[#This Row],[NC]]</f>
-        <v>0.26821477596925886</v>
-      </c>
-    </row>
-    <row r="11" spans="3:34" x14ac:dyDescent="0.2">
+        <v>0.27104015103118234</v>
+      </c>
+    </row>
+    <row r="11" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>9</v>
       </c>
@@ -28383,7 +28383,7 @@
         <v>4.0612075287078735E-4</v>
       </c>
     </row>
-    <row r="12" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -28439,7 +28439,7 @@
         <v>3.2461899785974599E-22</v>
       </c>
     </row>
-    <row r="13" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>11</v>
       </c>
@@ -28495,7 +28495,7 @@
         <v>0.28384118197935249</v>
       </c>
     </row>
-    <row r="14" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>96</v>
       </c>
@@ -28551,7 +28551,7 @@
         <v>3.9870125829944199E-3</v>
       </c>
     </row>
-    <row r="15" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>12</v>
       </c>
@@ -28607,7 +28607,7 @@
         <v>2.4727060379138801E-19</v>
       </c>
     </row>
-    <row r="16" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>98</v>
       </c>
@@ -28663,7 +28663,7 @@
         <v>3.8923102357539302E-4</v>
       </c>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>13</v>
       </c>
@@ -28719,7 +28719,7 @@
         <v>1.7644941803837761E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>14</v>
       </c>
@@ -28775,7 +28775,7 @@
         <v>0.29294823824970745</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -28831,7 +28831,7 @@
         <v>9.7879153888049406E-17</v>
       </c>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>99</v>
       </c>
@@ -28887,7 +28887,7 @@
         <v>2.5969210945285977E-18</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>100</v>
       </c>
@@ -28943,7 +28943,7 @@
         <v>1.2576648269261041E-3</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>16</v>
       </c>
@@ -28999,7 +28999,7 @@
         <v>0.31429615789629606</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>17</v>
       </c>
@@ -29055,7 +29055,7 @@
         <v>1.013584326646591E-2</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>18</v>
       </c>
@@ -29111,7 +29111,7 @@
         <v>1.130844790592713E-14</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>19</v>
       </c>
@@ -29167,7 +29167,7 @@
         <v>7.7633054778171915E-15</v>
       </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>101</v>
       </c>
@@ -29223,7 +29223,7 @@
         <v>1.3616766928883578E-3</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>20</v>
       </c>
@@ -29279,7 +29279,7 @@
         <v>0.35070089684878525</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>21</v>
       </c>
@@ -29335,7 +29335,7 @@
         <v>4.133145164997987E-3</v>
       </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>22</v>
       </c>
@@ -29391,7 +29391,7 @@
         <v>5.3033886785660525E-12</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>23</v>
       </c>
@@ -29447,7 +29447,7 @@
         <v>2.9121148863611918E-3</v>
       </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>24</v>
       </c>
@@ -29503,7 +29503,7 @@
         <v>2.842565662094408E-11</v>
       </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>25</v>
       </c>
@@ -29559,7 +29559,7 @@
         <v>0.38037984262174673</v>
       </c>
     </row>
-    <row r="33" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>26</v>
       </c>
@@ -29615,7 +29615,7 @@
         <v>2.9361732836270509E-3</v>
       </c>
     </row>
-    <row r="34" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>27</v>
       </c>
@@ -29671,7 +29671,7 @@
         <v>2.5214305980010281E-10</v>
       </c>
     </row>
-    <row r="35" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>28</v>
       </c>
@@ -29715,7 +29715,7 @@
         <v>7.5791563175681283E-4</v>
       </c>
     </row>
-    <row r="36" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>29</v>
       </c>
@@ -29747,7 +29747,7 @@
         <v>5.6680905306773525E-8</v>
       </c>
     </row>
-    <row r="37" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>30</v>
       </c>
@@ -29779,7 +29779,7 @@
         <v>0.40899805931452415</v>
       </c>
     </row>
-    <row r="38" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>31</v>
       </c>
@@ -29811,7 +29811,7 @@
         <v>3.7631744863843026E-4</v>
       </c>
     </row>
-    <row r="39" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>32</v>
       </c>
@@ -29843,7 +29843,7 @@
         <v>2.7356582288642847E-7</v>
       </c>
     </row>
-    <row r="40" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>33</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>1.2093808049619699E-4</v>
       </c>
     </row>
-    <row r="41" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>34</v>
       </c>
@@ -29907,7 +29907,7 @@
         <v>3.20009625918012E-6</v>
       </c>
     </row>
-    <row r="42" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>35</v>
       </c>
@@ -29939,7 +29939,7 @@
         <v>0.42981719241917432</v>
       </c>
     </row>
-    <row r="43" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>36</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>6.9080580120660573E-6</v>
       </c>
     </row>
-    <row r="44" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>37</v>
       </c>
@@ -30003,7 +30003,7 @@
         <v>1.821101629500186E-6</v>
       </c>
     </row>
-    <row r="45" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>102</v>
       </c>
@@ -30035,7 +30035,7 @@
         <v>3.0277794615519753E-6</v>
       </c>
     </row>
-    <row r="46" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>38</v>
       </c>
@@ -30067,7 +30067,7 @@
         <v>1.169927512054915E-5</v>
       </c>
     </row>
-    <row r="47" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>39</v>
       </c>
@@ -30099,7 +30099,7 @@
         <v>0.44029763257719456</v>
       </c>
     </row>
-    <row r="48" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>40</v>
       </c>
@@ -30131,7 +30131,7 @@
         <v>1.4529732759279445E-6</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>41</v>
       </c>
@@ -30163,7 +30163,7 @@
         <v>6.5916059743814033E-6</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>103</v>
       </c>
@@ -30195,7 +30195,7 @@
         <v>1.1853252176811144E-6</v>
       </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>42</v>
       </c>
@@ -30227,7 +30227,7 @@
         <v>1.7701272341279494E-5</v>
       </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>43</v>
       </c>
@@ -30259,7 +30259,7 @@
         <v>2.0576391716768572E-6</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>44</v>
       </c>
@@ -30291,7 +30291,7 @@
         <v>0.43748811591856085</v>
       </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>45</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>1.5899220563374749E-5</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>104</v>
       </c>
@@ -30355,7 +30355,7 @@
         <v>0.41427747096871592</v>
       </c>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>105</v>
       </c>
@@ -30387,7 +30387,7 @@
         <v>8.018208159456071E-5</v>
       </c>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>48</v>
       </c>
@@ -30419,7 +30419,7 @@
         <v>0.33560061217533704</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>49</v>
       </c>
@@ -30451,7 +30451,7 @@
         <v>3.6152721395822798E-4</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>50</v>
       </c>
@@ -30483,7 +30483,7 @@
         <v>0.22383007038523739</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>51</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>1.1706497287542517E-4</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>52</v>
       </c>
@@ -30547,7 +30547,7 @@
         <v>0.12400231291376168</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>53</v>
       </c>
@@ -30579,7 +30579,7 @@
         <v>1.6755127748873638E-2</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>54</v>
       </c>
@@ -30611,7 +30611,7 @@
         <v>8.1522833022556924E-3</v>
       </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>55</v>
       </c>
@@ -30643,7 +30643,7 @@
         <v>2.9582074947679775E-3</v>
       </c>
     </row>
-    <row r="65" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>56</v>
       </c>
@@ -30675,7 +30675,7 @@
         <v>5.6717579568383875E-4</v>
       </c>
     </row>
-    <row r="66" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>57</v>
       </c>
@@ -30707,7 +30707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>58</v>
       </c>
@@ -30739,7 +30739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>59</v>
       </c>
@@ -30771,7 +30771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>60</v>
       </c>
@@ -30803,7 +30803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>61</v>
       </c>
@@ -30835,7 +30835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>62</v>
       </c>
@@ -30867,7 +30867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D72" s="1">
         <v>28</v>
       </c>
@@ -30884,7 +30884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D73" s="1">
         <v>29</v>
       </c>
@@ -30901,7 +30901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D74" s="1">
         <v>30</v>
       </c>
@@ -30923,14 +30923,14 @@
       </c>
       <c r="AG74">
         <f>+SUM(AG4:AG71)</f>
-        <v>4.9252168545050159</v>
+        <v>4.9280422295669393</v>
       </c>
       <c r="AH74">
         <f>+SUM(AH4:AH71)</f>
-        <v>4.9252168545050159</v>
-      </c>
-    </row>
-    <row r="75" spans="3:34" x14ac:dyDescent="0.2">
+        <v>4.9280422295669393</v>
+      </c>
+    </row>
+    <row r="75" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D75" s="1">
         <v>31</v>
       </c>
@@ -30947,7 +30947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D76" s="1">
         <v>32</v>
       </c>
@@ -30964,7 +30964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D77" s="1">
         <v>33</v>
       </c>
@@ -30981,7 +30981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D78" s="1">
         <v>34</v>
       </c>
@@ -30998,7 +30998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D79" s="1">
         <v>35</v>
       </c>
@@ -31015,7 +31015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:34" x14ac:dyDescent="0.25">
       <c r="D80" s="1">
         <v>36</v>
       </c>
@@ -31032,7 +31032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D81" s="1">
         <v>37</v>
       </c>
@@ -31049,7 +31049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D82" s="1">
         <v>38</v>
       </c>
@@ -31066,7 +31066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D83" s="1">
         <v>39</v>
       </c>
@@ -31083,7 +31083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D84" s="1">
         <v>40</v>
       </c>
@@ -31100,7 +31100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D85" s="1">
         <v>41</v>
       </c>
@@ -31117,7 +31117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D86" s="1">
         <v>42</v>
       </c>
@@ -31134,7 +31134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D87" s="1">
         <v>43</v>
       </c>
@@ -31151,7 +31151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D88" s="1">
         <v>44</v>
       </c>
@@ -31168,7 +31168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D89" s="1">
         <v>45</v>
       </c>
@@ -31185,7 +31185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D90" s="1">
         <v>46</v>
       </c>
@@ -31202,7 +31202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D91" s="1">
         <v>48</v>
       </c>
@@ -31219,7 +31219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D92" s="1">
         <v>50</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D93" s="1">
         <v>51</v>
       </c>
@@ -31253,7 +31253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D94" s="1">
         <v>52</v>
       </c>
@@ -31270,7 +31270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D95" s="1">
         <v>54</v>
       </c>
